--- a/output/2026-10-10_10_Serbia_Podunavski_ATEX_Equipment-Services.xlsx
+++ b/output/2026-10-10_10_Serbia_Podunavski_ATEX_Equipment-Services.xlsx
@@ -552,7 +552,7 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Fuori dal distretto di Podunavski (Sabac e' nel distretto di Macva, Serbia occidentale) - allargamento regionale. Sede BIBUS Serbia confermata sul sito ufficiale (pagina rs-sr): indirizzo Cirila i Metodija 15, Sabac, telefono confermato. Linea di servo motori ExD (a marchio Moog) certificati ATEX e IECEx confermata sulla pagina prodotti ufficiale (motors-for-stationary-applications). Match ATEX diretto e confermato. Email "info@bibus.rs" presente nella lista grezza NON riscontrata sul sito ufficiale (solo form di contatto protetto anti-spam): lasciata vuota per policy anti-invenzione dati.</t>
+          <t>Fuori dal distretto di Podunavski (Sabac e' nel distretto di Macva, Serbia occidentale) - allargamento regionale. Sede BIBUS Serbia confermata sul sito ufficiale (pagina rs-sr): indirizzo Cirila i Metodija 15, Sabac, telefono confermato. Linea di servo motori ExD (a marchio Moog) certificati ATEX e IECEx confermata sulla pagina prodotti ufficiale (motors-for-stationary-applications). Match ATEX diretto e confermato. Email "info@bibus.rs" presente nella lista grezza NON riscontrata sul sito ufficiale (solo form di contatto protetto anti-spam): lasciata vuota per policy anti-invenzione dati. [DUPLICATO — vedi anche: 2026-10-07_04_Serbia_Mačvanski_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Fuori dal distretto di Podunavski (Belgrado) - allargamento regionale. Esistenza confermata SOLO tramite directory B2B terza parte (automa.net): distributore autorizzato dal 1994 per ASCO, AVENTICS, TOPWORX, GEORGIN, con menzione di "equipment for intrinsically safe explosion protection". Dominio ntrade.rs non risulta raggiungibile (DNS non risolve); nessuna fonte primaria ne' contatti telefono/email verificabili. Match ATEX plausibile ma NON confermato a fonte primaria - bassa confidenza, verificare manualmente con l'azienda prima di contattare.</t>
+          <t>Fuori dal distretto di Podunavski (Belgrado) - allargamento regionale. Esistenza confermata SOLO tramite directory B2B terza parte (automa.net): distributore autorizzato dal 1994 per ASCO, AVENTICS, TOPWORX, GEORGIN, con menzione di "equipment for intrinsically safe explosion protection". Dominio ntrade.rs non risulta raggiungibile (DNS non risolve); nessuna fonte primaria ne' contatti telefono/email verificabili. Match ATEX plausibile ma NON confermato a fonte primaria - bassa confidenza, verificare manualmente con l'azienda prima di contattare. [DUPLICATO — vedi anche: 2026-10-07_00_Serbia_Grad_Beograd_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
